--- a/data/stx_xlsx/KNOW.ST.xlsx
+++ b/data/stx_xlsx/KNOW.ST.xlsx
@@ -2616,7 +2616,7 @@
       <c r="U25" s="20">
         <v>44.51</v>
       </c>
-      <c r="V25" s="18"/>
+      <c r="V25" s="15"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
@@ -2644,9 +2644,7 @@
       <c r="S26" s="18"/>
       <c r="T26" s="18"/>
       <c r="U26" s="18"/>
-      <c r="V26" s="15">
-        <v>328.25</v>
-      </c>
+      <c r="V26" s="15"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
@@ -2710,7 +2708,9 @@
       <c r="U27" s="15">
         <v>303.71</v>
       </c>
-      <c r="V27" s="18"/>
+      <c r="V27" s="15">
+        <v>328.25</v>
+      </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">

--- a/data/stx_xlsx/KNOW.ST.xlsx
+++ b/data/stx_xlsx/KNOW.ST.xlsx
@@ -9424,12 +9424,24 @@
       <c r="B40" s="15">
         <v>504.63</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
+      <c r="C40" s="20">
+        <v>76.33</v>
+      </c>
+      <c r="D40" s="20">
+        <v>84.23</v>
+      </c>
+      <c r="E40" s="20">
+        <v>74.47</v>
+      </c>
+      <c r="F40" s="20">
+        <v>33.0</v>
+      </c>
+      <c r="G40" s="20">
+        <v>25.35</v>
+      </c>
+      <c r="H40" s="20">
+        <v>20.07</v>
+      </c>
       <c r="I40" s="20">
         <v>41.5</v>
       </c>
@@ -9457,11 +9469,26 @@
       <c r="Q40" s="20">
         <v>27.78</v>
       </c>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="18"/>
+      <c r="R40" s="20">
+        <f>SUM(R41,R45)</f>
+        <v>22.29</v>
+      </c>
+      <c r="S40" s="20">
+        <f t="shared" ref="S40:V40" si="1">SUM(S43:S44,S46)</f>
+        <v>23.33</v>
+      </c>
+      <c r="T40" s="20">
+        <f t="shared" si="1"/>
+        <v>17.51</v>
+      </c>
+      <c r="U40" s="20">
+        <f t="shared" si="1"/>
+        <v>12.29</v>
+      </c>
+      <c r="V40" s="20">
+        <f t="shared" si="1"/>
+        <v>10.75</v>
+      </c>
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
